--- a/Structure_Data/text.9.14/20260914_158/structure_factor_20260914_158.xlsx
+++ b/Structure_Data/text.9.14/20260914_158/structure_factor_20260914_158.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D330"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3325 @@
         <v>17.111671107815</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.286819458007812</v>
+      </c>
+      <c r="C30">
+        <v>0.285476684570312</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.286819458007812</v>
+      </c>
+      <c r="C31">
+        <v>0.285476684570312</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.223072052001953</v>
+      </c>
+      <c r="C32">
+        <v>0.172824859619141</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.130786895751953</v>
+      </c>
+      <c r="C33">
+        <v>0.0130500793457031</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.103134155273438</v>
+      </c>
+      <c r="C34">
+        <v>0.00878143310546875</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.0854682922363281</v>
+      </c>
+      <c r="C35">
+        <v>0.00827407836914062</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.040069580078125</v>
+      </c>
+      <c r="C36">
+        <v>0.00208663940429688</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0250930786132812</v>
+      </c>
+      <c r="C37">
+        <v>0.0008087158203125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.0191307067871094</v>
+      </c>
+      <c r="C38">
+        <v>0.00034332275390625</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.009429931640625</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.00673294067382812</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.00559234619140625</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.00516891479492188</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>22201</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>1.69334714652493</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1.54630358892845</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.05</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.1</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.15</v>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.2</v>
+      </c>
+      <c r="B62">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.25</v>
+      </c>
+      <c r="B63">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.3</v>
+      </c>
+      <c r="B64">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.35</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.4</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.45</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.5</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.55</v>
+      </c>
+      <c r="B69">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.6</v>
+      </c>
+      <c r="B70">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.65</v>
+      </c>
+      <c r="B71">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.75</v>
+      </c>
+      <c r="B73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.8</v>
+      </c>
+      <c r="B74">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.85</v>
+      </c>
+      <c r="B75">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.9</v>
+      </c>
+      <c r="B76">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.95</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.5</v>
+      </c>
+      <c r="B79">
+        <v>7286</v>
+      </c>
+      <c r="C79">
+        <v>0.328183415161479</v>
+      </c>
+      <c r="D79">
+        <v>0.328183415161479</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>1</v>
+      </c>
+      <c r="B80">
+        <v>4517</v>
+      </c>
+      <c r="C80">
+        <v>0.203459303634971</v>
+      </c>
+      <c r="D80">
+        <v>0.531642718796451</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>1.5</v>
+      </c>
+      <c r="B81">
+        <v>3057</v>
+      </c>
+      <c r="C81">
+        <v>0.137696500157651</v>
+      </c>
+      <c r="D81">
+        <v>0.669339218954101</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>2</v>
+      </c>
+      <c r="B82">
+        <v>2012</v>
+      </c>
+      <c r="C82">
+        <v>0.0906265483536778</v>
+      </c>
+      <c r="D82">
+        <v>0.759965767307779</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>2.5</v>
+      </c>
+      <c r="B83">
+        <v>1420</v>
+      </c>
+      <c r="C83">
+        <v>0.0639610828341066</v>
+      </c>
+      <c r="D83">
+        <v>0.823926850141885</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84">
+        <v>977</v>
+      </c>
+      <c r="C84">
+        <v>0.0440070267105085</v>
+      </c>
+      <c r="D84">
+        <v>0.867933876852394</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>3.5</v>
+      </c>
+      <c r="B85">
+        <v>785</v>
+      </c>
+      <c r="C85">
+        <v>0.03535876762308</v>
+      </c>
+      <c r="D85">
+        <v>0.903292644475474</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86">
+        <v>548</v>
+      </c>
+      <c r="C86">
+        <v>0.0246835728120355</v>
+      </c>
+      <c r="D86">
+        <v>0.92797621728751</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>4.5</v>
+      </c>
+      <c r="B87">
+        <v>438</v>
+      </c>
+      <c r="C87">
+        <v>0.0197288410431963</v>
+      </c>
+      <c r="D87">
+        <v>0.947705058330706</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>5</v>
+      </c>
+      <c r="B88">
+        <v>293</v>
+      </c>
+      <c r="C88">
+        <v>0.0131976037115445</v>
+      </c>
+      <c r="D88">
+        <v>0.96090266204225</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>5.5</v>
+      </c>
+      <c r="B89">
+        <v>238</v>
+      </c>
+      <c r="C89">
+        <v>0.0107202378271249</v>
+      </c>
+      <c r="D89">
+        <v>0.971622899869375</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>6</v>
+      </c>
+      <c r="B90">
+        <v>174</v>
+      </c>
+      <c r="C90">
+        <v>0.00783748479798207</v>
+      </c>
+      <c r="D90">
+        <v>0.979460384667357</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>6.5</v>
+      </c>
+      <c r="B91">
+        <v>125</v>
+      </c>
+      <c r="C91">
+        <v>0.00563037701004459</v>
+      </c>
+      <c r="D91">
+        <v>0.985090761677402</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>7</v>
+      </c>
+      <c r="B92">
+        <v>72</v>
+      </c>
+      <c r="C92">
+        <v>0.00324309715778569</v>
+      </c>
+      <c r="D92">
+        <v>0.988333858835188</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>7.5</v>
+      </c>
+      <c r="B93">
+        <v>59</v>
+      </c>
+      <c r="C93">
+        <v>0.00265753794874105</v>
+      </c>
+      <c r="D93">
+        <v>0.990991396783929</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="B94">
+        <v>42</v>
+      </c>
+      <c r="C94">
+        <v>0.00189180667537498</v>
+      </c>
+      <c r="D94">
+        <v>0.992883203459304</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>8.5</v>
+      </c>
+      <c r="B95">
+        <v>45</v>
+      </c>
+      <c r="C95">
+        <v>0.00202693572361605</v>
+      </c>
+      <c r="D95">
+        <v>0.99491013918292</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>9</v>
+      </c>
+      <c r="B96">
+        <v>37</v>
+      </c>
+      <c r="C96">
+        <v>0.0016665915949732</v>
+      </c>
+      <c r="D96">
+        <v>0.996576730777893</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>9.5</v>
+      </c>
+      <c r="B97">
+        <v>25</v>
+      </c>
+      <c r="C97">
+        <v>0.00112607540200892</v>
+      </c>
+      <c r="D97">
+        <v>0.997702806179902</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>10</v>
+      </c>
+      <c r="B98">
+        <v>18</v>
+      </c>
+      <c r="C98">
+        <v>0.000810774289446421</v>
+      </c>
+      <c r="D98">
+        <v>0.998513580469348</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>10.5</v>
+      </c>
+      <c r="B99">
+        <v>10</v>
+      </c>
+      <c r="C99">
+        <v>0.000450430160803567</v>
+      </c>
+      <c r="D99">
+        <v>0.998964010630152</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>11</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
+      </c>
+      <c r="C100">
+        <v>0.00027025809648214</v>
+      </c>
+      <c r="D100">
+        <v>0.999234268726634</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>11.5</v>
+      </c>
+      <c r="B101">
+        <v>8</v>
+      </c>
+      <c r="C101">
+        <v>0.000360344128642854</v>
+      </c>
+      <c r="D101">
+        <v>0.999594612855277</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>12</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>4.50430160803567e-05</v>
+      </c>
+      <c r="D102">
+        <v>0.999639655871357</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>12.5</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103">
+        <v>9.00860321607135e-05</v>
+      </c>
+      <c r="D103">
+        <v>0.999729741903518</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>13</v>
+      </c>
+      <c r="B104">
+        <v>2</v>
+      </c>
+      <c r="C104">
+        <v>9.00860321607135e-05</v>
+      </c>
+      <c r="D104">
+        <v>0.999819827935679</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>13.5</v>
+      </c>
+      <c r="B105">
+        <v>3</v>
+      </c>
+      <c r="C105">
+        <v>0.00013512904824107</v>
+      </c>
+      <c r="D105">
+        <v>0.99995495698392</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>20.5</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>4.50430160803567e-05</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>186956</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.779064993094636</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.303286802709347</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.05</v>
+      </c>
+      <c r="B121">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.1</v>
+      </c>
+      <c r="B122">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.15</v>
+      </c>
+      <c r="B123">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.2</v>
+      </c>
+      <c r="B124">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.25</v>
+      </c>
+      <c r="B125">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.3</v>
+      </c>
+      <c r="B126">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>0.35</v>
+      </c>
+      <c r="B127">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.4</v>
+      </c>
+      <c r="B128">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.45</v>
+      </c>
+      <c r="B129">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0.5</v>
+      </c>
+      <c r="B130">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>0.55</v>
+      </c>
+      <c r="B131">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>0.6</v>
+      </c>
+      <c r="B132">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>0.65</v>
+      </c>
+      <c r="B133">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>0.7</v>
+      </c>
+      <c r="B134">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>0.75</v>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>0.8</v>
+      </c>
+      <c r="B136">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>0.85</v>
+      </c>
+      <c r="B137">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>0.9</v>
+      </c>
+      <c r="B138">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>0.95</v>
+      </c>
+      <c r="B139">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>0.5</v>
+      </c>
+      <c r="B141">
+        <v>73983</v>
+      </c>
+      <c r="C141">
+        <v>0.395724127602217</v>
+      </c>
+      <c r="D141">
+        <v>0.395724127602217</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B142">
+        <v>41876</v>
+      </c>
+      <c r="C142">
+        <v>0.22398853206102</v>
+      </c>
+      <c r="D142">
+        <v>0.619712659663236</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B143">
+        <v>16986</v>
+      </c>
+      <c r="C143">
+        <v>0.0908556023877276</v>
+      </c>
+      <c r="D143">
+        <v>0.710568262050964</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>1</v>
+      </c>
+      <c r="B144">
+        <v>12823</v>
+      </c>
+      <c r="C144">
+        <v>0.0685883309441794</v>
+      </c>
+      <c r="D144">
+        <v>0.779156592995143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B145">
+        <v>21761</v>
+      </c>
+      <c r="C145">
+        <v>0.116396371338711</v>
+      </c>
+      <c r="D145">
+        <v>0.895552964333854</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B146">
+        <v>8450</v>
+      </c>
+      <c r="C146">
+        <v>0.0451978005520015</v>
+      </c>
+      <c r="D146">
+        <v>0.940750764885856</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B147">
+        <v>4293</v>
+      </c>
+      <c r="C147">
+        <v>0.0229626222212713</v>
+      </c>
+      <c r="D147">
+        <v>0.963713387107127</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>1.5</v>
+      </c>
+      <c r="B148">
+        <v>3815</v>
+      </c>
+      <c r="C148">
+        <v>0.0204058709001048</v>
+      </c>
+      <c r="D148">
+        <v>0.984119258007232</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B149">
+        <v>1269</v>
+      </c>
+      <c r="C149">
+        <v>0.00678769336100473</v>
+      </c>
+      <c r="D149">
+        <v>0.990906951368236</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B150">
+        <v>626</v>
+      </c>
+      <c r="C150">
+        <v>0.00334838143734355</v>
+      </c>
+      <c r="D150">
+        <v>0.99425533280558</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B151">
+        <v>167</v>
+      </c>
+      <c r="C151">
+        <v>0.000893258306767368</v>
+      </c>
+      <c r="D151">
+        <v>0.995148591112347</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B152">
+        <v>393</v>
+      </c>
+      <c r="C152">
+        <v>0.0021020988895783</v>
+      </c>
+      <c r="D152">
+        <v>0.997250690001926</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B153">
+        <v>325</v>
+      </c>
+      <c r="C153">
+        <v>0.00173837694430775</v>
+      </c>
+      <c r="D153">
+        <v>0.998989066946233</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2</v>
+      </c>
+      <c r="B154">
+        <v>30</v>
+      </c>
+      <c r="C154">
+        <v>0.000160465564089946</v>
+      </c>
+      <c r="D154">
+        <v>0.999149532510323</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B155">
+        <v>115</v>
+      </c>
+      <c r="C155">
+        <v>0.000615117995678127</v>
+      </c>
+      <c r="D155">
+        <v>0.999764650506001</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B156">
+        <v>25</v>
+      </c>
+      <c r="C156">
+        <v>0.000133721303408289</v>
+      </c>
+      <c r="D156">
+        <v>0.99989837180941</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B157">
+        <v>8</v>
+      </c>
+      <c r="C157">
+        <v>4.27908170906523e-05</v>
+      </c>
+      <c r="D157">
+        <v>0.9999411626265</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B158">
+        <v>6</v>
+      </c>
+      <c r="C158">
+        <v>3.20931128179893e-05</v>
+      </c>
+      <c r="D158">
+        <v>0.999973255739318</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159">
+        <v>1.06977042726631e-05</v>
+      </c>
+      <c r="D159">
+        <v>0.999983953443591</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160">
+        <v>1.60465564089946e-05</v>
+      </c>
+      <c r="D160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.286819458007812</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>0</v>
+      </c>
+      <c r="B172">
+        <v>0.286819458007812</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>0.5</v>
+      </c>
+      <c r="B173">
+        <v>0.202800750732422</v>
+      </c>
+      <c r="C173">
+        <v>6</v>
+      </c>
+      <c r="D173">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>1</v>
+      </c>
+      <c r="B174">
+        <v>0.168020982008714</v>
+      </c>
+      <c r="C174">
+        <v>26</v>
+      </c>
+      <c r="D174">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>1.5</v>
+      </c>
+      <c r="B175">
+        <v>0.130840131971571</v>
+      </c>
+      <c r="C175">
+        <v>90</v>
+      </c>
+      <c r="D175">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2</v>
+      </c>
+      <c r="B176">
+        <v>0.108501548197732</v>
+      </c>
+      <c r="C176">
+        <v>134</v>
+      </c>
+      <c r="D176">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2.5</v>
+      </c>
+      <c r="B177">
+        <v>0.0951420392176902</v>
+      </c>
+      <c r="C177">
+        <v>258</v>
+      </c>
+      <c r="D177">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>3</v>
+      </c>
+      <c r="B178">
+        <v>0.0900065166194264</v>
+      </c>
+      <c r="C178">
+        <v>410</v>
+      </c>
+      <c r="D178">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>3.5</v>
+      </c>
+      <c r="B179">
+        <v>0.0898460975060096</v>
+      </c>
+      <c r="C179">
+        <v>494</v>
+      </c>
+      <c r="D179">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>4</v>
+      </c>
+      <c r="B180">
+        <v>0.0897646033245584</v>
+      </c>
+      <c r="C180">
+        <v>690</v>
+      </c>
+      <c r="D180">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>4.5</v>
+      </c>
+      <c r="B181">
+        <v>0.0884426457966192</v>
+      </c>
+      <c r="C181">
+        <v>962</v>
+      </c>
+      <c r="D181">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>5</v>
+      </c>
+      <c r="B182">
+        <v>0.086647985628611</v>
+      </c>
+      <c r="C182">
+        <v>1098</v>
+      </c>
+      <c r="D182">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>5.5</v>
+      </c>
+      <c r="B183">
+        <v>0.0853678891872444</v>
+      </c>
+      <c r="C183">
+        <v>1406</v>
+      </c>
+      <c r="D183">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>6</v>
+      </c>
+      <c r="B184">
+        <v>0.0847147807422246</v>
+      </c>
+      <c r="C184">
+        <v>1578</v>
+      </c>
+      <c r="D184">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>6.5</v>
+      </c>
+      <c r="B185">
+        <v>0.0843928727451472</v>
+      </c>
+      <c r="C185">
+        <v>2018</v>
+      </c>
+      <c r="D185">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>7</v>
+      </c>
+      <c r="B186">
+        <v>0.0841365361396926</v>
+      </c>
+      <c r="C186">
+        <v>2342</v>
+      </c>
+      <c r="D186">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>7.5</v>
+      </c>
+      <c r="B187">
+        <v>0.0837971593904604</v>
+      </c>
+      <c r="C187">
+        <v>2634</v>
+      </c>
+      <c r="D187">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>8</v>
+      </c>
+      <c r="B188">
+        <v>0.083510761456278</v>
+      </c>
+      <c r="C188">
+        <v>2930</v>
+      </c>
+      <c r="D188">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>8.5</v>
+      </c>
+      <c r="B189">
+        <v>0.0832658461582513</v>
+      </c>
+      <c r="C189">
+        <v>3402</v>
+      </c>
+      <c r="D189">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>9</v>
+      </c>
+      <c r="B190">
+        <v>0.0830148258685337</v>
+      </c>
+      <c r="C190">
+        <v>3926</v>
+      </c>
+      <c r="D190">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>9.5</v>
+      </c>
+      <c r="B191">
+        <v>0.0828925614283222</v>
+      </c>
+      <c r="C191">
+        <v>4266</v>
+      </c>
+      <c r="D191">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>10</v>
+      </c>
+      <c r="B192">
+        <v>0.0827291944314259</v>
+      </c>
+      <c r="C192">
+        <v>4730</v>
+      </c>
+      <c r="D192">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>10.5</v>
+      </c>
+      <c r="B193">
+        <v>0.0826426871242627</v>
+      </c>
+      <c r="C193">
+        <v>5510</v>
+      </c>
+      <c r="D193">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>11</v>
+      </c>
+      <c r="B194">
+        <v>0.082518968853064</v>
+      </c>
+      <c r="C194">
+        <v>5562</v>
+      </c>
+      <c r="D194">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>11.5</v>
+      </c>
+      <c r="B195">
+        <v>0.0823990498987635</v>
+      </c>
+      <c r="C195">
+        <v>6410</v>
+      </c>
+      <c r="D195">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>12</v>
+      </c>
+      <c r="B196">
+        <v>0.0823215543272739</v>
+      </c>
+      <c r="C196">
+        <v>6894</v>
+      </c>
+      <c r="D196">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>12.5</v>
+      </c>
+      <c r="B197">
+        <v>0.0821981738183463</v>
+      </c>
+      <c r="C197">
+        <v>7490</v>
+      </c>
+      <c r="D197">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>13</v>
+      </c>
+      <c r="B198">
+        <v>0.0820657984631262</v>
+      </c>
+      <c r="C198">
+        <v>8258</v>
+      </c>
+      <c r="D198">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>13.5</v>
+      </c>
+      <c r="B199">
+        <v>0.0820284956477604</v>
+      </c>
+      <c r="C199">
+        <v>8994</v>
+      </c>
+      <c r="D199">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>14</v>
+      </c>
+      <c r="B200">
+        <v>0.081996097116432</v>
+      </c>
+      <c r="C200">
+        <v>9446</v>
+      </c>
+      <c r="D200">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>14.5</v>
+      </c>
+      <c r="B201">
+        <v>0.0819663955587547</v>
+      </c>
+      <c r="C201">
+        <v>9978</v>
+      </c>
+      <c r="D201">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>15</v>
+      </c>
+      <c r="B202">
+        <v>0.081906553444132</v>
+      </c>
+      <c r="C202">
+        <v>11138</v>
+      </c>
+      <c r="D202">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>15.5</v>
+      </c>
+      <c r="B203">
+        <v>0.0818311499646311</v>
+      </c>
+      <c r="C203">
+        <v>11406</v>
+      </c>
+      <c r="D203">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>16</v>
+      </c>
+      <c r="B204">
+        <v>0.0817599426633558</v>
+      </c>
+      <c r="C204">
+        <v>12575</v>
+      </c>
+      <c r="D204">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>16.5</v>
+      </c>
+      <c r="B205">
+        <v>0.0817767412843621</v>
+      </c>
+      <c r="C205">
+        <v>12848</v>
+      </c>
+      <c r="D205">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>17</v>
+      </c>
+      <c r="B206">
+        <v>0.0818786190912301</v>
+      </c>
+      <c r="C206">
+        <v>12060</v>
+      </c>
+      <c r="D206">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>17.5</v>
+      </c>
+      <c r="B207">
+        <v>0.0820072352462039</v>
+      </c>
+      <c r="C207">
+        <v>11804</v>
+      </c>
+      <c r="D207">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>18</v>
+      </c>
+      <c r="B208">
+        <v>0.0821572063448815</v>
+      </c>
+      <c r="C208">
+        <v>11016</v>
+      </c>
+      <c r="D208">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>18.5</v>
+      </c>
+      <c r="B209">
+        <v>0.0822256997366932</v>
+      </c>
+      <c r="C209">
+        <v>10700</v>
+      </c>
+      <c r="D209">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>19</v>
+      </c>
+      <c r="B210">
+        <v>0.0822176376098783</v>
+      </c>
+      <c r="C210">
+        <v>9756</v>
+      </c>
+      <c r="D210">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>19.5</v>
+      </c>
+      <c r="B211">
+        <v>0.082170477351828</v>
+      </c>
+      <c r="C211">
+        <v>9224</v>
+      </c>
+      <c r="D211">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>20</v>
+      </c>
+      <c r="B212">
+        <v>0.082169231520053</v>
+      </c>
+      <c r="C212">
+        <v>8408</v>
+      </c>
+      <c r="D212">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>20.5</v>
+      </c>
+      <c r="B213">
+        <v>0.0821651299026661</v>
+      </c>
+      <c r="C213">
+        <v>7452</v>
+      </c>
+      <c r="D213">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>21</v>
+      </c>
+      <c r="B214">
+        <v>0.0820547970858487</v>
+      </c>
+      <c r="C214">
+        <v>7040</v>
+      </c>
+      <c r="D214">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>21.5</v>
+      </c>
+      <c r="B215">
+        <v>0.0818931671352321</v>
+      </c>
+      <c r="C215">
+        <v>5820</v>
+      </c>
+      <c r="D215">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>22</v>
+      </c>
+      <c r="B216">
+        <v>0.0816549738899606</v>
+      </c>
+      <c r="C216">
+        <v>4880</v>
+      </c>
+      <c r="D216">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>22.5</v>
+      </c>
+      <c r="B217">
+        <v>0.0813877194877562</v>
+      </c>
+      <c r="C217">
+        <v>3936</v>
+      </c>
+      <c r="D217">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>23</v>
+      </c>
+      <c r="B218">
+        <v>0.0808491212362129</v>
+      </c>
+      <c r="C218">
+        <v>2999</v>
+      </c>
+      <c r="D218">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>23.5</v>
+      </c>
+      <c r="B219">
+        <v>0.0803319983526107</v>
+      </c>
+      <c r="C219">
+        <v>2180</v>
+      </c>
+      <c r="D219">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>24</v>
+      </c>
+      <c r="B220">
+        <v>0.0797685081576124</v>
+      </c>
+      <c r="C220">
+        <v>1620</v>
+      </c>
+      <c r="D220">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>24.5</v>
+      </c>
+      <c r="B221">
+        <v>0.0791436062743332</v>
+      </c>
+      <c r="C221">
+        <v>1208</v>
+      </c>
+      <c r="D221">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>25</v>
+      </c>
+      <c r="B222">
+        <v>0.0788711256282345</v>
+      </c>
+      <c r="C222">
+        <v>942</v>
+      </c>
+      <c r="D222">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>25.5</v>
+      </c>
+      <c r="B223">
+        <v>0.0786942782467359</v>
+      </c>
+      <c r="C223">
+        <v>584</v>
+      </c>
+      <c r="D223">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>26</v>
+      </c>
+      <c r="B224">
+        <v>0.0783710211095676</v>
+      </c>
+      <c r="C224">
+        <v>284</v>
+      </c>
+      <c r="D224">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>26.5</v>
+      </c>
+      <c r="B225">
+        <v>0.0780735413233439</v>
+      </c>
+      <c r="C225">
+        <v>192</v>
+      </c>
+      <c r="D225">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>27</v>
+      </c>
+      <c r="B226">
+        <v>0.0777810903695913</v>
+      </c>
+      <c r="C226">
+        <v>104</v>
+      </c>
+      <c r="D226">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>27.5</v>
+      </c>
+      <c r="B227">
+        <v>0.077967643737793</v>
+      </c>
+      <c r="C227">
+        <v>24</v>
+      </c>
+      <c r="D227">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>28</v>
+      </c>
+      <c r="B228">
+        <v>0.0778961181640625</v>
+      </c>
+      <c r="C228">
+        <v>1</v>
+      </c>
+      <c r="D228">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>0</v>
+      </c>
+      <c r="B230">
+        <v>0.286819458007812</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>0.5</v>
+      </c>
+      <c r="B231">
+        <v>0.202129364013672</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>1</v>
+      </c>
+      <c r="B232">
+        <v>0.151218414306641</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>1.5</v>
+      </c>
+      <c r="B233">
+        <v>0.119194030761719</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>2</v>
+      </c>
+      <c r="B234">
+        <v>0.100013732910156</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>2.5</v>
+      </c>
+      <c r="B235">
+        <v>0.0911483764648438</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>3</v>
+      </c>
+      <c r="B236">
+        <v>0.0902633666992188</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>3.5</v>
+      </c>
+      <c r="B237">
+        <v>0.0889968872070312</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>4</v>
+      </c>
+      <c r="B238">
+        <v>0.0868873596191406</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>4.5</v>
+      </c>
+      <c r="B239">
+        <v>0.0838127136230469</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>5</v>
+      </c>
+      <c r="B240">
+        <v>0.0821266174316406</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>5.5</v>
+      </c>
+      <c r="B241">
+        <v>0.0811500549316406</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>6</v>
+      </c>
+      <c r="B242">
+        <v>0.0815048217773438</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>6.5</v>
+      </c>
+      <c r="B243">
+        <v>0.0815467834472656</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>7</v>
+      </c>
+      <c r="B244">
+        <v>0.0818748474121094</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>7.5</v>
+      </c>
+      <c r="B245">
+        <v>0.0815849304199219</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>8</v>
+      </c>
+      <c r="B246">
+        <v>0.081787109375</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>8.5</v>
+      </c>
+      <c r="B247">
+        <v>0.0815658569335938</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>9</v>
+      </c>
+      <c r="B248">
+        <v>0.0814628601074219</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>9.5</v>
+      </c>
+      <c r="B249">
+        <v>0.0813217163085938</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>10</v>
+      </c>
+      <c r="B250">
+        <v>0.0817527770996094</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>10.5</v>
+      </c>
+      <c r="B251">
+        <v>0.0825958251953125</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>11</v>
+      </c>
+      <c r="B252">
+        <v>0.0834579467773438</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>11.5</v>
+      </c>
+      <c r="B253">
+        <v>0.08404541015625</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>12</v>
+      </c>
+      <c r="B254">
+        <v>0.0844841003417969</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>12.5</v>
+      </c>
+      <c r="B255">
+        <v>0.0840606689453125</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>13</v>
+      </c>
+      <c r="B256">
+        <v>0.0838508605957031</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>13.5</v>
+      </c>
+      <c r="B257">
+        <v>0.0830726623535156</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>14</v>
+      </c>
+      <c r="B258">
+        <v>0.0821571350097656</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>14.5</v>
+      </c>
+      <c r="B259">
+        <v>0.0816459655761719</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>15</v>
+      </c>
+      <c r="B260">
+        <v>0.0813560485839844</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>15.5</v>
+      </c>
+      <c r="B261">
+        <v>0.0815963745117188</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>16</v>
+      </c>
+      <c r="B262">
+        <v>0.0816268920898438</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>0</v>
+      </c>
+      <c r="B264">
+        <v>0.286819458007812</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>0.5</v>
+      </c>
+      <c r="B265">
+        <v>0.202278137207031</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>1</v>
+      </c>
+      <c r="B266">
+        <v>0.152088165283203</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>1.5</v>
+      </c>
+      <c r="B267">
+        <v>0.120586395263672</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>2</v>
+      </c>
+      <c r="B268">
+        <v>0.101146697998047</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>2.5</v>
+      </c>
+      <c r="B269">
+        <v>0.0923843383789062</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>3</v>
+      </c>
+      <c r="B270">
+        <v>0.091888427734375</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>3.5</v>
+      </c>
+      <c r="B271">
+        <v>0.0916061401367188</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>4</v>
+      </c>
+      <c r="B272">
+        <v>0.0905723571777344</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>4.5</v>
+      </c>
+      <c r="B273">
+        <v>0.0885696411132812</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>5</v>
+      </c>
+      <c r="B274">
+        <v>0.0865364074707031</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>5.5</v>
+      </c>
+      <c r="B275">
+        <v>0.0856781005859375</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>6</v>
+      </c>
+      <c r="B276">
+        <v>0.0853157043457031</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>6.5</v>
+      </c>
+      <c r="B277">
+        <v>0.0849456787109375</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>7</v>
+      </c>
+      <c r="B278">
+        <v>0.0846633911132812</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>7.5</v>
+      </c>
+      <c r="B279">
+        <v>0.0844078063964844</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>8</v>
+      </c>
+      <c r="B280">
+        <v>0.0837135314941406</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>8.5</v>
+      </c>
+      <c r="B281">
+        <v>0.083160400390625</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>9</v>
+      </c>
+      <c r="B282">
+        <v>0.0832099914550781</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>9.5</v>
+      </c>
+      <c r="B283">
+        <v>0.0832595825195312</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>10</v>
+      </c>
+      <c r="B284">
+        <v>0.0829505920410156</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>10.5</v>
+      </c>
+      <c r="B285">
+        <v>0.0824546813964844</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>11</v>
+      </c>
+      <c r="B286">
+        <v>0.0823440551757812</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>11.5</v>
+      </c>
+      <c r="B287">
+        <v>0.0825996398925781</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>12</v>
+      </c>
+      <c r="B288">
+        <v>0.0831756591796875</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>12.5</v>
+      </c>
+      <c r="B289">
+        <v>0.0832786560058594</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>13</v>
+      </c>
+      <c r="B290">
+        <v>0.0826873779296875</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>13.5</v>
+      </c>
+      <c r="B291">
+        <v>0.0825347900390625</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>14</v>
+      </c>
+      <c r="B292">
+        <v>0.0829696655273438</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>14.5</v>
+      </c>
+      <c r="B293">
+        <v>0.0836181640625</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>15</v>
+      </c>
+      <c r="B294">
+        <v>0.083770751953125</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>15.5</v>
+      </c>
+      <c r="B295">
+        <v>0.0840568542480469</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>16</v>
+      </c>
+      <c r="B296">
+        <v>0.0840911865234375</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>0</v>
+      </c>
+      <c r="B298">
+        <v>0.286819458007812</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>0.5</v>
+      </c>
+      <c r="B299">
+        <v>0.203994750976562</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>1</v>
+      </c>
+      <c r="B300">
+        <v>0.154144287109375</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>1.5</v>
+      </c>
+      <c r="B301">
+        <v>0.121604919433594</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>2</v>
+      </c>
+      <c r="B302">
+        <v>0.101741790771484</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>2.5</v>
+      </c>
+      <c r="B303">
+        <v>0.0922126770019531</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>3</v>
+      </c>
+      <c r="B304">
+        <v>0.0906906127929688</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>3.5</v>
+      </c>
+      <c r="B305">
+        <v>0.0904998779296875</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>4</v>
+      </c>
+      <c r="B306">
+        <v>0.0904884338378906</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>4.5</v>
+      </c>
+      <c r="B307">
+        <v>0.0889129638671875</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>5</v>
+      </c>
+      <c r="B308">
+        <v>0.0868377685546875</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>5.5</v>
+      </c>
+      <c r="B309">
+        <v>0.08502197265625</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>6</v>
+      </c>
+      <c r="B310">
+        <v>0.0837364196777344</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>6.5</v>
+      </c>
+      <c r="B311">
+        <v>0.0826568603515625</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>7</v>
+      </c>
+      <c r="B312">
+        <v>0.082244873046875</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>7.5</v>
+      </c>
+      <c r="B313">
+        <v>0.0824394226074219</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>8</v>
+      </c>
+      <c r="B314">
+        <v>0.082733154296875</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>8.5</v>
+      </c>
+      <c r="B315">
+        <v>0.0823631286621094</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>9</v>
+      </c>
+      <c r="B316">
+        <v>0.0821266174316406</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>9.5</v>
+      </c>
+      <c r="B317">
+        <v>0.0820960998535156</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>10</v>
+      </c>
+      <c r="B318">
+        <v>0.0825119018554688</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>10.5</v>
+      </c>
+      <c r="B319">
+        <v>0.0830078125</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>11</v>
+      </c>
+      <c r="B320">
+        <v>0.0834999084472656</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>11.5</v>
+      </c>
+      <c r="B321">
+        <v>0.0833511352539062</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>12</v>
+      </c>
+      <c r="B322">
+        <v>0.0828323364257812</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>12.5</v>
+      </c>
+      <c r="B323">
+        <v>0.0823135375976562</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>13</v>
+      </c>
+      <c r="B324">
+        <v>0.0817031860351562</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>13.5</v>
+      </c>
+      <c r="B325">
+        <v>0.0809593200683594</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>14</v>
+      </c>
+      <c r="B326">
+        <v>0.08135986328125</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>14.5</v>
+      </c>
+      <c r="B327">
+        <v>0.0822067260742188</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>15</v>
+      </c>
+      <c r="B328">
+        <v>0.0828208923339844</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>15.5</v>
+      </c>
+      <c r="B329">
+        <v>0.0830230712890625</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>16</v>
+      </c>
+      <c r="B330">
+        <v>0.0828170776367187</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>